--- a/framework/fw_popsizes.xlsx
+++ b/framework/fw_popsizes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://burnetinstitute.sharepoint.com/sites/WG-Modelling-HepatitisB/Shared Documents/Applications/Australia Optimisation/Framework Development/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://burnetinstitute-my.sharepoint.com/personal/chris_seaman_burnet_edu_au/Documents/Documents/GitRepos/burnet-hbv/framework/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="13_ncr:1_{7D9B31DB-38E3-D74D-81CE-1D7B61EA513E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA6A7D78-EB25-4289-9D9A-401E5E0631DF}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="13_ncr:1_{7D9B31DB-38E3-D74D-81CE-1D7B61EA513E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62E23F43-8C5B-402B-BF93-3CAD1902C788}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" firstSheet="3" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="9" r:id="rId1"/>
@@ -2967,7 +2967,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="63">
   <si>
     <t>Datasheet Code Name</t>
   </si>
@@ -3128,22 +3128,10 @@
     <t>acm_rate</t>
   </si>
   <si>
-    <t>arrivals</t>
-  </si>
-  <si>
-    <t>departures</t>
-  </si>
-  <si>
     <t>Annual Livebirths</t>
   </si>
   <si>
     <t>number</t>
-  </si>
-  <si>
-    <t>Annual Overseas Arrivals</t>
-  </si>
-  <si>
-    <t>Annual Oversease Departures</t>
   </si>
   <si>
     <t>All Cause (non HepB) Mortality Rate</t>
@@ -3158,18 +3146,6 @@
     <t>Total Population Size</t>
   </si>
   <si>
-    <t>bos_arrive</t>
-  </si>
-  <si>
-    <t>bos_depart</t>
-  </si>
-  <si>
-    <t>% of departures by country of birth</t>
-  </si>
-  <si>
-    <t>% of arrivals by country of birth</t>
-  </si>
-  <si>
     <t>pop_arrive</t>
   </si>
   <si>
@@ -3180,12 +3156,6 @@
   </si>
   <si>
     <t>Total Departures by broad pop group</t>
-  </si>
-  <si>
-    <t>max(bos_arrive*pop_arrive, 0)</t>
-  </si>
-  <si>
-    <t>max(bos_depart*pop_depart, 0)</t>
   </si>
 </sst>
 </file>
@@ -5682,7 +5652,7 @@
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>52</v>
@@ -5695,7 +5665,7 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -8105,7 +8075,7 @@
   <sheetPr>
     <tabColor theme="5" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q5"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" style="4" customWidth="1"/>
@@ -8182,10 +8152,10 @@
         <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -8199,12 +8169,14 @@
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
@@ -8217,12 +8189,14 @@
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -8235,79 +8209,15 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="K5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" s="2"/>
-      <c r="N5" s="2"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="K6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="N6" s="2"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="2" t="s">
         <v>41</v>
       </c>
     </row>
@@ -8323,13 +8233,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
+    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{3C5E5528-F961-4CFC-83ED-CB90A50DF965}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I1048576 O2:P1048576" xr:uid="{7CB7BECB-8CCA-402C-8209-B57AEC65D6EC}">
       <formula1>"n,y"</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D1048576" xr:uid="{7B357739-ECEB-45D0-9FF6-C94815526279}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1" xr:uid="{3C5E5528-F961-4CFC-83ED-CB90A50DF965}"/>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576" xr:uid="{23A69AD6-56EA-4510-BE84-B964156BC5E6}">
       <formula1>"rate, probability, number, proportion, duration"</formula1>
     </dataValidation>
@@ -8438,10 +8348,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>43</v>
@@ -8598,25 +8508,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100856A3DB4B0A5FF4A85E5854FA9B1BD84" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="79455fcbefce608407f5707fa152ecb6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4" xmlns:ns3="d27fc6f8-d518-4cdb-8bab-875cbacf3583" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="58fab150063022ddbbdee2e062213d03" ns2:_="" ns3:_="">
     <xsd:import namespace="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
@@ -8827,25 +8718,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF11C12E-4E0B-4E94-9902-D38A64A3A452}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55C5AB9-D676-4791-93EC-CF0F822DC0A7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7C0B1D3-C0E1-40DE-AAB1-A47468E73433}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8862,4 +8754,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E55C5AB9-D676-4791-93EC-CF0F822DC0A7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF11C12E-4E0B-4E94-9902-D38A64A3A452}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5de2aea6-bdc3-4e5f-b0ae-84d85b5764e4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>